--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>subontology</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:050523</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -634,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>behavioural BCI engagement frequency statistic</t>
+          <t>behavioural BCI engagement duration statistic</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -642,22 +642,22 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -668,33 +668,33 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement frequency</t>
+          <t>median behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -705,33 +705,33 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement frequency</t>
+          <t>maximum behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -742,33 +742,33 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement frequency</t>
+          <t>minimum behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -779,33 +779,33 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement frequency</t>
+          <t>mean behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>The mean duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -815,7 +815,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>behavioural BCI engagement frequency</t>
+          <t>BCI engagement period statistic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -823,33 +823,22 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -857,27 +846,31 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BCI engagement period statistic</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>maximum BCI engagement period</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,23 +896,23 @@
           <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>The median period of intervention that participants engaged with.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -930,33 +923,33 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mean BCI engagement period</t>
+          <t>minimum BCI engagement period</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>The minimum period of intervention that participants engaged with.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -967,33 +960,33 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>maximum BCI engagement period</t>
+          <t>mean BCI engagement period</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>The mean period of intervention  that participants engaged with.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1001,36 +994,32 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>minimum BCI engagement period</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1038,42 +1027,36 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>number of behavioural BCI engagements</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050523</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1081,32 +1064,36 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1117,33 +1104,33 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement duration</t>
+          <t>mean aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>BCIO:050539</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1154,33 +1141,33 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement duration</t>
+          <t>median aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>The median duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1188,36 +1175,43 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1225,36 +1219,32 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1262,32 +1252,36 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050539</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1298,33 +1292,33 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>median aggregate behavioural BCI engagement duration</t>
+          <t>mean behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>The median duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1335,33 +1329,33 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
+          <t>maximum behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1372,33 +1366,33 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
+          <t>minimum behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1406,36 +1400,42 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>number of behavioural BCI engagements</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>behavioural BCI engagement number statistic</t>
+          <t>behavioural BCI engagement frequency statistic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1453,22 +1453,22 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1479,33 +1479,33 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement number</t>
+          <t>maximum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1516,33 +1516,33 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>median behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>The median frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1553,33 +1553,33 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement number</t>
+          <t>minimum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1590,28 +1590,28 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement number</t>
+          <t>mean behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>The median number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1641,14 +1641,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>temporal region</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1657,11 +1657,16 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BCIO:040000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1669,7 +1674,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
+          <t>individual human activity</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1679,277 +1684,307 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>A process that is produced by a person.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050916</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>participant engagement with intervention</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:013025</t>
+          <t>BCIO:013000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>participant engagement with behaviour change intervention</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>A 30-minute session, 1 hour spent 'logged in'</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
+          <t>This is distinguished from engagement that involves thought processes.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A cognitive BCI engagement that involves attending.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Paying attention to certain images or information within the intervention</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through comprehension</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>mental process</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through judging</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MFOEM:000195</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1957,24 +1992,47 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>affective process</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Enjoying or liking the intervention</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MFOEM:000001</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1983,31 +2041,41 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>emotion process</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through satisfaction</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2019,23 +2087,33 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>emotional BCI engagement through fear</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+          <t>Emotional BCI engagement that involves fear.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2047,28 +2125,38 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>emotional BCI engagement through enjoyment</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2080,20 +2168,33 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>emotional BCI engagement through mistrust</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+          <t>Emotional BCI engagement that involves mistrust.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2103,96 +2204,92 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>jouissance</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.</t>
+          <t>Emotional BCI engagement that involves interest.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>mistrust</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>MF:0000020</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MF:0000008</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2202,7 +2299,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>cognitive process</t>
+          <t>judging</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2210,27 +2307,22 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:006110</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2238,32 +2330,37 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>comprehension</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>attending</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
+          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Focusing on particular internal or external stimuli.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>MFOEM:000195</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2273,7 +2370,7 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>attending</t>
+          <t>affective process</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2281,27 +2378,14 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A mental process whereby relevant aspects of one's mental experience are focused on specific targets.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Focusing on particular internal or external stimuli.</t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>MFOEM:000001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2309,95 +2393,85 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>judging</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>emotion process</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:040000</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>individual human activity</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A process that is produced by a person.</t>
-        </is>
-      </c>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050916</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>participant engagement with intervention</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:013000</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2405,32 +2479,32 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>participant engagement with behaviour change intervention</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>jouissance</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2439,41 +2513,31 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2485,42 +2549,28 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement through attention</t>
+          <t>mistrust</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Paying attention to an intervention’s content</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2532,38 +2582,28 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement through judging</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>MF:0000008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2571,41 +2611,37 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>cognitive process</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through comprehension</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
+          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
-        </is>
-      </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BCIO:006110</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2616,291 +2652,255 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>emotional BCI engagement</t>
+          <t>comprehension</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Enjoying or liking the intervention</t>
-        </is>
-      </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through fear</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>BCIO:013025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through mistrust</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
+          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>A unit of time that describes the length of an engagement event.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>A 30-minute session, 1 hour spent 'logged in'</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through interest</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BCI engagement period</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through satisfaction</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>

--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>informaldefinition</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>subontology</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -542,21 +542,21 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -567,14 +567,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>bodily process</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,14 +592,14 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>MF:0000020</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -608,7 +608,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>mental process</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -617,14 +617,14 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050523</t>
+          <t>MF:0000008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -634,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>behavioural BCI engagement duration statistic</t>
+          <t>cognitive process</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -642,22 +642,27 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>BCIO:006110</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -668,33 +673,29 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement duration</t>
+          <t>comprehension</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -702,36 +703,37 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>attending</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A mental process whereby relevant aspects of one's mental experience are focused on specific targets.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Focusing on particular internal or external stimuli.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -739,36 +741,32 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>judging</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>MFOEM:000195</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -776,36 +774,24 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>affective process</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>MFOEM:000001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -813,32 +799,32 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>BCI engagement period statistic</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>emotion process</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -847,35 +833,31 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>maximum BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>mistrust</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050538</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -884,35 +866,23 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>median BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>The median period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -921,35 +891,31 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>minimum BCI engagement period</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>jouissance</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -958,35 +924,26 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>mean BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -994,32 +951,32 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1028,109 +985,94 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:040000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>individual human activity</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A process that is produced by a person.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:050916</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>participant engagement with intervention</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050539</t>
+          <t>BCIO:013000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1138,36 +1080,32 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>median aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>participant engagement with behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>The median duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1175,43 +1113,42 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1219,32 +1156,41 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement number statistic</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through comprehension</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1253,35 +1199,45 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves attending.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The median number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>Paying attention to certain images or information within the intervention</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1290,35 +1246,41 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through judging</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1329,33 +1291,43 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>behavioural BCI engagement</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>This is distinguished from engagement that involves thought processes.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1366,33 +1338,44 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement number</t>
+          <t>emotional BCI engagement</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>Enjoying or liking the intervention</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1400,42 +1383,37 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>number of behavioural BCI engagements</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through mistrust</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves mistrust.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1443,32 +1421,42 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency statistic</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through enjoyment</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1477,35 +1465,43 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves interest.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1514,35 +1510,41 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through satisfaction</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1551,82 +1553,66 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through fear</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves fear.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1634,64 +1620,118 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:040000</t>
+          <t>BCIO:013025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>individual human activity</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A process that is produced by a person.</t>
+          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>A 30-minute session, 1 hour spent 'logged in'</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the length of an engagement event.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050916</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1700,7 +1740,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>participant engagement with intervention</t>
+          <t>BCI engagement period</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1709,239 +1749,173 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:013000</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>participant engagement with behaviour change intervention</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through attention</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Paying attention to an intervention’s content</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through comprehension</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>BCIO:050523</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1949,42 +1923,32 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through judging</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1995,44 +1959,33 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>emotional BCI engagement</t>
+          <t>mean behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Enjoying or liking the intervention</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>The mean duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2041,41 +1994,35 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through satisfaction</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2084,36 +2031,35 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through fear</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2122,41 +2068,35 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2164,37 +2104,32 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>BCI engagement period statistic</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through mistrust</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2203,93 +2138,109 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through interest</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>maximum BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:050538</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>median BCI engagement period</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>The median period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>mental process</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>minimum BCI engagement period</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>The minimum period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2297,32 +2248,36 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>judging</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>mean BCI engagement period</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>The mean period of intervention  that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2332,7 +2287,7 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>attending</t>
+          <t>behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2340,27 +2295,33 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Focusing on particular internal or external stimuli.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MFOEM:000195</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2370,7 +2331,7 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>affective process</t>
+          <t>number of behavioural BCI engagements</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2378,14 +2339,32 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A mental process that has positive or negative valence.</t>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MFOEM:000001</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2393,32 +2372,32 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>emotion process</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2427,26 +2406,35 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>mean aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>BCIO:050539</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2455,23 +2443,35 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>happiness</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>median aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>The median duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2480,31 +2480,35 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>jouissance</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2513,31 +2517,35 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2545,32 +2553,32 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>mistrust</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2579,31 +2587,35 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement number</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MF:0000008</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2611,37 +2623,36 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>cognitive process</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:006110</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2652,255 +2663,244 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>median behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency statistic</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:013025</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>A 30-minute session, 1 hour spent 'logged in'</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>The median frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>

--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -442,27 +442,27 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>subontology</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -524,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>occurrent</t>
+          <t>continuant</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -542,21 +542,21 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -567,14 +567,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>bodily process</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,14 +592,14 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -608,7 +608,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>mental process</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -617,14 +617,14 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MF:0000008</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -634,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>cognitive process</t>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -642,27 +642,22 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:006110</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -673,29 +668,33 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -703,37 +702,36 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>attending</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mean aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A mental process whereby relevant aspects of one's mental experience are focused on specific targets.</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Focusing on particular internal or external stimuli.</t>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -741,32 +739,36 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>judging</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MFOEM:000195</t>
+          <t>BCIO:050539</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -774,24 +776,36 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>affective process</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>median aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>The median duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MFOEM:000001</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -799,32 +813,32 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>emotion process</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -833,31 +847,35 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>mistrust</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement number</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -866,23 +884,35 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>happiness</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement number</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -891,31 +921,35 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>jouissance</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.</t>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -924,26 +958,35 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement number</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -951,32 +994,42 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>number of behavioural BCI engagements</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -984,95 +1037,106 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency statistic</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:040000</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>individual human activity</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A process that is produced by a person.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050916</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>participant engagement with intervention</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:013000</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1080,32 +1144,36 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>participant engagement with behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>The median frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1116,39 +1184,33 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement</t>
+          <t>maximum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1156,41 +1218,43 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through comprehension</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1198,46 +1262,32 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BCI engagement period statistic</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through attention</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Paying attention to an intervention’s content</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1246,41 +1296,35 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through judging</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>minimum BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
+          <t>The minimum period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>BCIO:050538</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1291,43 +1335,33 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>behavioural BCI engagement</t>
+          <t>median BCI engagement period</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
+          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
+          <t>The median period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1338,44 +1372,33 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>emotional BCI engagement</t>
+          <t>mean BCI engagement period</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Enjoying or liking the intervention</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
+          <t>The mean period of intervention  that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1384,36 +1407,35 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through mistrust</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>maximum BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
+      <c r="M29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BCIO:050523</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1421,42 +1443,32 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1465,43 +1477,35 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through interest</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
+          <t>The mean duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1510,41 +1514,35 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through satisfaction</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1553,66 +1551,82 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through fear</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
+      <c r="M33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>temporal interval</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1620,262 +1634,257 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:013025</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>A 30-minute session, 1 hour spent 'logged in'</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BCI engagement period</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>continuant</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:013025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the length of an engagement event.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 30-minute session, 1 hour spent 'logged in'</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1883,72 +1892,64 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050523</t>
+          <t>MF:0000020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1956,36 +1957,37 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>attending</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
+          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Focusing on particular internal or external stimuli.</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1993,36 +1995,32 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>judging</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>MF:0000008</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2030,36 +2028,37 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>cognitive process</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>BCIO:006110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2070,33 +2069,29 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement duration</t>
+          <t>comprehension</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
+          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>MFOEM:000195</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2106,7 +2101,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BCI engagement period statistic</t>
+          <t>affective process</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2114,22 +2109,14 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>MFOEM:000001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2140,33 +2127,29 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>maximum BCI engagement period</t>
+          <t>emotion process</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:050538</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2175,35 +2158,26 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>median BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>The median period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2212,35 +2186,31 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>minimum BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>mistrust</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2249,35 +2219,31 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>mean BCI engagement period</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2285,43 +2251,32 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2329,42 +2284,24 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>number of behavioural BCI engagements</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2372,106 +2309,95 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Genuss</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:040000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>individual human activity</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
+          <t>A process that is produced by a person.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050539</t>
+          <t>BCIO:050916</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>participant engagement with intervention</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>median aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>The median duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:013000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2479,36 +2405,32 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>participant engagement with behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2519,33 +2441,39 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
+          <t>cognitive BCI engagement</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2553,32 +2481,46 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement number statistic</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+          <t>A cognitive BCI engagement that involves attending.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Paying attention to certain images or information within the intervention</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2587,35 +2529,40 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through comprehension</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2624,35 +2571,41 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through judging</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2663,33 +2616,43 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement number</t>
+          <t>behavioural BCI engagement</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>The median number of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>This is distinguished from engagement that involves thought processes.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2700,33 +2663,44 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>emotional BCI engagement</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Enjoying or liking the intervention</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2734,32 +2708,42 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency statistic</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through enjoyment</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2768,35 +2752,36 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through mistrust</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
+          <t>Emotional BCI engagement that involves mistrust.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2805,35 +2790,43 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+          <t>Emotional BCI engagement that involves interest.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2842,35 +2835,41 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through satisfaction</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2879,28 +2878,29 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through fear</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
+          <t>Emotional BCI engagement that involves fear.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
         </is>
       </c>
     </row>

--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>synonyms</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -634,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
+          <t>number of behavioural BCI engagements</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -642,22 +642,32 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -665,36 +675,32 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BCI engagement period statistic</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -705,33 +711,33 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
+          <t>maximum BCI engagement period</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>BCIO:050538</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -742,33 +748,33 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
+          <t>median BCI engagement period</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>The median period of intervention that participants engaged with.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050539</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -779,33 +785,33 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>median aggregate behavioural BCI engagement duration</t>
+          <t>minimum BCI engagement period</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>The minimum period of intervention that participants engaged with.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>The median duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -813,32 +819,36 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement number statistic</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mean BCI engagement period</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>The mean period of intervention  that participants engaged with.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -846,36 +856,43 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement number</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -883,36 +900,32 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement number</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -923,33 +936,33 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>mean behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -960,33 +973,33 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement number</t>
+          <t>maximum behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>The median number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -994,42 +1007,36 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>number of behavioural BCI engagements</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1037,32 +1044,36 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency statistic</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1070,36 +1081,32 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>BCIO:050539</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1110,33 +1117,33 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement frequency</t>
+          <t>median aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>The median duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1147,33 +1154,33 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement frequency</t>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1184,33 +1191,33 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement frequency</t>
+          <t>mean aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1218,43 +1225,36 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BCI engagement period statistic</t>
+          <t>behavioural BCI engagement frequency statistic</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1272,22 +1272,22 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1298,33 +1298,33 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>minimum BCI engagement period</t>
+          <t>minimum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050538</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1335,33 +1335,33 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>median BCI engagement period</t>
+          <t>mean behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>The median period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1372,33 +1372,33 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>mean BCI engagement period</t>
+          <t>median behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>The median frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1409,28 +1409,28 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>maximum BCI engagement period</t>
+          <t>maximum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1456,19 +1456,19 @@
           <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1479,33 +1479,33 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement duration</t>
+          <t>minimum behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1516,33 +1516,33 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement duration</t>
+          <t>median behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1553,33 +1553,33 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement duration</t>
+          <t>mean behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>The mean duration of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1590,28 +1590,28 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement duration</t>
+          <t>maximum behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1641,14 +1641,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>temporal region</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1657,11 +1657,16 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BCIO:040000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1669,7 +1674,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
+          <t>individual human activity</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1679,277 +1684,302 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
+          <t>A process that is produced by a person.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050916</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>temporal interval</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>participant engagement with intervention</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BCIO:013000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>participant engagement with behaviour change intervention</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+          <t>Enjoying or liking the intervention</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:013025</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through enjoyment</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 30-minute session, 1 hour spent 'logged in'</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through fear</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
-        </is>
-      </c>
+          <t>Emotional BCI engagement that involves fear.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
-        </is>
-      </c>
+          <t>Emotional BCI engagement that involves interest.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>mental process</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through satisfaction</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
-        </is>
-      </c>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1957,37 +1987,37 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>attending</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through mistrust</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>Emotional BCI engagement that involves mistrust.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Focusing on particular internal or external stimuli.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1995,32 +2025,42 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>judging</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MF:0000008</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2028,37 +2068,46 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>cognitive process</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves attending.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
+          <t>Paying attention to certain images or information within the intervention</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:006110</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2067,31 +2116,40 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>comprehension</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through comprehension</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MFOEM:000195</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2099,24 +2157,42 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>affective process</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through judging</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
-        </is>
-      </c>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MFOEM:000001</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2127,90 +2203,93 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>emotion process</t>
+          <t>behavioural BCI engagement</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>This is distinguished from engagement that involves thought processes.</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+          <t>A process in which at least one bodily component of an organism participates.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>MF:0000020</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>mistrust</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
+          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>MFOEM:000195</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2218,32 +2297,24 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>affective process</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>MFOEM:000001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2252,31 +2323,31 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>emotion process</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2288,20 +2359,23 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
-        </is>
-      </c>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2311,93 +2385,88 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Genuss</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:040000</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>individual human activity</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A process that is produced by a person.</t>
-        </is>
-      </c>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050916</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>participant engagement with intervention</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:013000</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2405,32 +2474,32 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>participant engagement with behaviour change intervention</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>enjoyment</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2439,41 +2508,31 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>mistrust</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2481,46 +2540,32 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>judging</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through attention</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Paying attention to an intervention’s content</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>MF:0000008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2528,41 +2573,37 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>cognitive process</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through comprehension</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>BCIO:006110</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2571,41 +2612,31 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through judging</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>comprehension</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2613,296 +2644,265 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>attending</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Focusing on particular internal or external stimuli.</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Enjoying or liking the intervention</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through mistrust</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:013025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through interest</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+          <t>A 30-minute session, 1 hour spent 'logged in'</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
-        </is>
-      </c>
+          <t>A unit of time that describes the length of an engagement event.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through satisfaction</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
-        </is>
-      </c>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BCI engagement period</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through fear</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
-        </is>
-      </c>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -447,27 +447,27 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -634,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>number of behavioural BCI engagements</t>
+          <t>BCI engagement period statistic</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -642,32 +642,22 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -675,32 +665,36 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BCI engagement period statistic</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>maximum BCI engagement period</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -711,33 +705,33 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>maximum BCI engagement period</t>
+          <t>minimum BCI engagement period</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>The minimum period of intervention that participants engaged with.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050538</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -748,33 +742,33 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>median BCI engagement period</t>
+          <t>mean BCI engagement period</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>The median period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>The mean period of intervention  that participants engaged with.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>BCIO:050538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -785,33 +779,33 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>minimum BCI engagement period</t>
+          <t>median BCI engagement period</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>The median period of intervention that participants engaged with.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -819,36 +813,32 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>mean BCI engagement period</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -856,43 +846,36 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -900,32 +883,36 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement number statistic</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -936,33 +923,33 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement number</t>
+          <t>minimum behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -973,33 +960,33 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>mean behavioural BCI engagement number</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1007,36 +994,32 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement number</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1047,33 +1030,33 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement number</t>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>The median number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1081,27 +1064,31 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1127,23 +1114,23 @@
           <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>The median duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1154,33 +1141,33 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
+          <t>mean aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:050523</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1188,36 +1175,32 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1228,33 +1211,33 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
+          <t>median behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1262,32 +1245,36 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency statistic</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1298,33 +1285,33 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement frequency</t>
+          <t>mean behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>The mean duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1335,33 +1322,33 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement frequency</t>
+          <t>maximum behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1369,36 +1356,42 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>number of behavioural BCI engagements</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1406,36 +1399,32 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency statistic</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050523</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1443,32 +1432,36 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1479,33 +1472,33 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement duration</t>
+          <t>median behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>The median frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1516,33 +1509,33 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>median behavioural BCI engagement duration</t>
+          <t>minimum behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1553,33 +1546,33 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement duration</t>
+          <t>mean behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1587,31 +1580,38 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1659,7 +1659,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
@@ -1712,18 +1712,18 @@
           <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1750,19 +1750,19 @@
           <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1773,44 +1773,43 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>emotional BCI engagement</t>
+          <t>behavioural BCI engagement</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Enjoying or liking the intervention</t>
-        </is>
-      </c>
+          <t>This is distinguished from engagement that involves thought processes.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1819,41 +1818,46 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Enjoying or liking the intervention</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1865,33 +1869,38 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>emotional BCI engagement through fear</t>
+          <t>emotional BCI engagement through satisfaction</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1903,40 +1912,33 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>emotional BCI engagement through interest</t>
+          <t>emotional BCI engagement through mistrust</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
+          <t>Emotional BCI engagement that involves mistrust.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1948,38 +1950,38 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>emotional BCI engagement through satisfaction</t>
+          <t>emotional BCI engagement through enjoyment</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1991,33 +1993,33 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>emotional BCI engagement through mistrust</t>
+          <t>emotional BCI engagement through fear</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
+          <t>Emotional BCI engagement that involves fear.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2026,41 +2028,43 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+          <t>Emotional BCI engagement that involves interest.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2069,45 +2073,41 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through attention</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Paying attention to an intervention’s content</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2119,37 +2119,38 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement through comprehension</t>
+          <t>cognitive BCI engagement through judging</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2161,38 +2162,37 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement through judging</t>
+          <t>cognitive BCI engagement through comprehension</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2201,40 +2201,40 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
+          <t>A cognitive BCI engagement that involves attending.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
-        </is>
-      </c>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Paying attention to certain images or information within the intervention</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2257,7 +2257,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
     </row>
@@ -2332,22 +2332,22 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2359,23 +2359,28 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>mistrust</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2387,28 +2392,20 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2418,30 +2415,30 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>jouissance</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli. [Source: OCEAS]</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2453,20 +2450,28 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
-        </is>
-      </c>
+          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2476,30 +2481,25 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>enjoyment</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2511,28 +2511,28 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>mistrust</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>judging</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2550,16 +2550,21 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Focusing on particular internal or external stimuli.</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2586,18 +2591,18 @@
           <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2624,19 +2629,19 @@
           <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2646,7 +2651,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>attending</t>
+          <t>judging</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2654,21 +2659,16 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Focusing on particular internal or external stimuli.</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2694,7 +2694,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2712,54 +2712,65 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>temporal interval</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2791,28 +2802,28 @@
 Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the length of an engagement event.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>A 30-minute session, 1 hour spent 'logged in'</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2821,7 +2832,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>aggregate behavioural BCI engagement duration</t>
+          <t>BCI engagement period</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2830,79 +2841,68 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
-        </is>
-      </c>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -567,7 +567,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A mental process that has positive or negative valence.</t>
+          <t>A &lt;mental process&gt; that has positive or negative valence.</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>jouissance</t>
+          <t>enjoyment</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -2456,7 +2456,7 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Satisfaction is an emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
+          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
